--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.08009037487974</v>
+        <v>6.350514685917958</v>
       </c>
       <c r="D2" t="n">
-        <v>29.54996239892326</v>
+        <v>4.801868889825029</v>
       </c>
       <c r="E2" t="n">
-        <v>8.93924986522989</v>
+        <v>1.452628103099857</v>
       </c>
       <c r="F2" t="n">
-        <v>7.113051446877505</v>
+        <v>1.155870860117595</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.12192854738762</v>
+        <v>8.957313388950489</v>
       </c>
       <c r="D3" t="n">
-        <v>36.26907080650437</v>
+        <v>5.89372400605696</v>
       </c>
       <c r="E3" t="n">
-        <v>8.93924986522989</v>
+        <v>1.452628103099857</v>
       </c>
       <c r="F3" t="n">
-        <v>7.113051446877505</v>
+        <v>1.155870860117595</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.80937605600437</v>
+        <v>10.36902360910071</v>
       </c>
       <c r="D4" t="n">
-        <v>35.86798239629448</v>
+        <v>5.828547139397853</v>
       </c>
       <c r="E4" t="n">
-        <v>8.93924986522989</v>
+        <v>1.452628103099857</v>
       </c>
       <c r="F4" t="n">
-        <v>7.113051446877505</v>
+        <v>1.155870860117595</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.1255466251886</v>
+        <v>8.145401326593149</v>
       </c>
       <c r="D5" t="n">
-        <v>49.12607047934829</v>
+        <v>7.982986452894097</v>
       </c>
       <c r="E5" t="n">
-        <v>8.93924986522989</v>
+        <v>1.452628103099857</v>
       </c>
       <c r="F5" t="n">
-        <v>7.113051446877505</v>
+        <v>1.155870860117595</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
